--- a/dcf/SNOW.xlsx
+++ b/dcf/SNOW.xlsx
@@ -1138,184 +1138,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>3.643755233819425</v>
+        <v>13.46874780952567</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>3.419954499474586</v>
+        <v>12.79959773586688</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>3.211070569228815</v>
+        <v>12.16746950698194</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>3.016212829028678</v>
+        <v>11.57028096900649</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>2.834545092352451</v>
+        <v>11.00607366397129</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>2.665282108311191</v>
+        <v>10.47300502070707</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>2.507686306258512</v>
+        <v>9.969341069267845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>4.62625449139005</v>
+        <v>14.4512470670963</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>4.357918823113816</v>
+        <v>13.73756205950611</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>4.106710463004127</v>
+        <v>13.06310940075725</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>3.871619643026458</v>
+        <v>12.42568778300427</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>3.651697949514335</v>
+        <v>11.82322652113317</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>3.44605439955078</v>
+        <v>11.25377731194666</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>3.253851782559446</v>
+        <v>10.71550654556878</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>5.608753748960672</v>
+        <v>15.43374632466692</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>5.295883146753043</v>
+        <v>14.67552638314533</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>5.002350356779439</v>
+        <v>13.95874929453256</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>4.727026457024238</v>
+        <v>13.28109459700205</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>4.468850806676219</v>
+        <v>12.64037937829505</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>4.226826690790366</v>
+        <v>12.03454960318624</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>4.000017258860378</v>
+        <v>11.46167202186971</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>6.591253006531296</v>
+        <v>16.41624558223754</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>6.233847470392272</v>
+        <v>15.61349070678456</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>5.89799025055475</v>
+        <v>14.85438918830787</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>5.582433271022018</v>
+        <v>14.13650141099983</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>5.286003663838101</v>
+        <v>13.45753223545693</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>5.007598982029954</v>
+        <v>12.81532189442583</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>4.746182735161311</v>
+        <v>12.20783749817064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>7.573752264101923</v>
+        <v>17.39874483980816</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>7.171811794031501</v>
+        <v>16.55145503042379</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>6.793630144330062</v>
+        <v>15.75002908208318</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>6.437840085019801</v>
+        <v>14.99190822499761</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>6.103156520999983</v>
+        <v>14.27468509261882</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>5.788371273269543</v>
+        <v>13.59609418566542</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>5.492348211462244</v>
+        <v>12.95400297447158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>8.556251521672545</v>
+        <v>18.38124409737879</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>8.10977611767073</v>
+        <v>17.48941935406302</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>7.689270038105374</v>
+        <v>16.64566897585849</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>7.293246899017581</v>
+        <v>15.84731503899539</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>6.920309378161868</v>
+        <v>15.0918379497807</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>6.569143564509131</v>
+        <v>14.37686647690501</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>6.238513687763177</v>
+        <v>13.70016845077251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>9.53875077924317</v>
+        <v>19.36374335494942</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>9.047740441309958</v>
+        <v>18.42738367770225</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>8.584909931880686</v>
+        <v>17.54130886963381</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>8.148653713015362</v>
+        <v>16.70272185299317</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>7.737462235323752</v>
+        <v>15.90899080694259</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>7.349915855748721</v>
+        <v>15.1576387681446</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>6.984679164064111</v>
+        <v>14.44633392707344</v>
       </c>
     </row>
     <row r="13">
@@ -1338,7 +1338,7 @@
         <v>0.09037446571294339</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.09111010870322031</v>
+        <v>0.1293284635918243</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24401,7 +24401,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>5.582433271022018</v>
+        <v>14.13650141099983</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>18.0290901802935</v>
+        <v>32.75212926404321</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>-2.255913923205896</v>
+        <v>1.707158460329075</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/SNOW.xlsx
+++ b/dcf/SNOW.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>13.46874780952567</v>
+        <v>10.6041753740565</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>12.79959773586688</v>
+        <v>10.07694475536901</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>12.16746950698194</v>
+        <v>9.579420439524741</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>11.57028096900649</v>
+        <v>9.109922658161331</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>11.00607366397129</v>
+        <v>8.666871656693349</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>10.47300502070707</v>
+        <v>8.248781373351818</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>9.969341069267845</v>
+        <v>7.854253542236896</v>
       </c>
     </row>
     <row r="6">
@@ -1167,25 +1167,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>14.4512470670963</v>
+        <v>11.40093439614124</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>13.73756205950611</v>
+        <v>10.83758811615998</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>13.06310940075725</v>
+        <v>10.30574075010594</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>12.42568778300427</v>
+        <v>9.803615901544262</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>11.82322652113317</v>
+        <v>9.329542805143804</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>11.25377731194666</v>
+        <v>8.881949655613029</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>10.71550654556878</v>
+        <v>8.459357383924214</v>
       </c>
     </row>
     <row r="7">
@@ -1193,25 +1193,25 @@
         <v>21</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>15.43374632466692</v>
+        <v>12.19769341822597</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>14.67552638314533</v>
+        <v>11.59823147695096</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>13.95874929453256</v>
+        <v>11.03206106068713</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>13.28109459700205</v>
+        <v>10.49730914492719</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>12.64037937829505</v>
+        <v>9.992213953594261</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>12.03454960318624</v>
+        <v>9.515117937874239</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>11.46167202186971</v>
+        <v>9.064461225611526</v>
       </c>
     </row>
     <row r="8">
@@ -1219,25 +1219,25 @@
         <v>22</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>16.41624558223754</v>
+        <v>12.9944524403107</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>15.61349070678456</v>
+        <v>12.35887483774193</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>14.85438918830787</v>
+        <v>11.75838137126833</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>14.13650141099983</v>
+        <v>11.19100238831012</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>13.45753223545693</v>
+        <v>10.65488510204472</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>12.81532189442583</v>
+        <v>10.14828622013546</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>12.20783749817064</v>
+        <v>9.669565067298837</v>
       </c>
     </row>
     <row r="9">
@@ -1245,25 +1245,25 @@
         <v>23</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>17.39874483980816</v>
+        <v>13.79121146239542</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>16.55145503042379</v>
+        <v>13.11951819853291</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>15.75002908208318</v>
+        <v>12.48470168184952</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>14.99190822499761</v>
+        <v>11.88469563169305</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>14.27468509261882</v>
+        <v>11.31755625049517</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>13.59609418566542</v>
+        <v>10.78145450239667</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>12.95400297447158</v>
+        <v>10.27466890898615</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>18.38124409737879</v>
+        <v>14.58797048448015</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>17.48941935406302</v>
+        <v>13.88016155932388</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>16.64566897585849</v>
+        <v>13.21102199243071</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>15.84731503899539</v>
+        <v>12.57838887507598</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>15.0918379497807</v>
+        <v>11.98022739894563</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>14.37686647690501</v>
+        <v>11.41462278465788</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>13.70016845077251</v>
+        <v>10.87977275067347</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>25</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>19.36374335494942</v>
+        <v>15.38472950656488</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>18.42738367770225</v>
+        <v>14.64080492011485</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>17.54130886963381</v>
+        <v>13.93734230301191</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>16.70272185299317</v>
+        <v>13.27208211845891</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>15.90899080694259</v>
+        <v>12.64289854739608</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>15.1576387681446</v>
+        <v>12.04779106691909</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>14.44633392707344</v>
+        <v>11.48487659236078</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.1293284635918243</v>
+        <v>0.1263059909619966</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>14.13650141099983</v>
+        <v>11.19100238831012</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>32.75212926404321</v>
+        <v>25.78611820799028</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>1.707158460329075</v>
+        <v>1.089841237817762</v>
       </c>
     </row>
     <row r="59">

--- a/dcf/SNOW.xlsx
+++ b/dcf/SNOW.xlsx
@@ -412,22 +412,22 @@
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>10.6041753740565</v>
+        <v>97.31944657826206</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>10.07694475536901</v>
+        <v>93.33602890368817</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>9.579420439524741</v>
+        <v>89.54515879551786</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>9.109922658161331</v>
+        <v>85.93662288688883</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>8.666871656693349</v>
+        <v>82.50079525733614</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>8.248781373351818</v>
+        <v>79.22860109428078</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>7.854253542236896</v>
+        <v>76.111482756889</v>
       </c>
     </row>
     <row r="6">
@@ -1167,25 +1167,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>11.40093439614124</v>
+        <v>101.3642912931248</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>10.83758811615998</v>
+        <v>97.1975280427135</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>10.30574075010594</v>
+        <v>93.23241276832498</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>9.803615901544262</v>
+        <v>89.45824155885796</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>9.329542805143804</v>
+        <v>85.86492646665531</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>8.881949655613029</v>
+        <v>82.44295739164899</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>8.459357383924214</v>
+        <v>79.18336648603467</v>
       </c>
     </row>
     <row r="7">
@@ -1193,25 +1193,25 @@
         <v>21</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>12.19769341822597</v>
+        <v>105.4091360079876</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>11.59823147695096</v>
+        <v>101.0590271817388</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>11.03206106068713</v>
+        <v>96.91966674113212</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>10.49730914492719</v>
+        <v>92.9798602308271</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>9.992213953594261</v>
+        <v>89.22905767597447</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>9.515117937874239</v>
+        <v>85.65731368901723</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>9.064461225611526</v>
+        <v>82.25525021518033</v>
       </c>
     </row>
     <row r="8">
@@ -1219,25 +1219,25 @@
         <v>22</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>12.9944524403107</v>
+        <v>109.4539807228504</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>12.35887483774193</v>
+        <v>104.9205263207641</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>11.75838137126833</v>
+        <v>100.6069207139392</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>11.19100238831012</v>
+        <v>96.50147890279625</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>10.65488510204472</v>
+        <v>92.59318888529367</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>10.14828622013546</v>
+        <v>88.87166998638544</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>9.669565067298837</v>
+        <v>85.32713394432599</v>
       </c>
     </row>
     <row r="9">
@@ -1245,25 +1245,25 @@
         <v>23</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>13.79121146239542</v>
+        <v>113.4988254377131</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>13.11951819853291</v>
+        <v>108.7820254597894</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>12.48470168184952</v>
+        <v>104.2941746867463</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>11.88469563169305</v>
+        <v>100.0230975747654</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>11.31755625049517</v>
+        <v>95.95732009461284</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>10.78145450239667</v>
+        <v>92.08602628375365</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>10.27466890898615</v>
+        <v>88.39901767347163</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>14.58797048448015</v>
+        <v>117.5436701525759</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>13.88016155932388</v>
+        <v>112.6435245988147</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>13.21102199243071</v>
+        <v>107.9814286595535</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>12.57838887507598</v>
+        <v>103.5447162467345</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>11.98022739894563</v>
+        <v>99.32145130393202</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>11.41462278465788</v>
+        <v>95.30038258112189</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>10.87977275067347</v>
+        <v>91.4709014026173</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>25</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>15.38472950656488</v>
+        <v>121.5885148674387</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>14.64080492011485</v>
+        <v>116.50502373784</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>13.93734230301191</v>
+        <v>111.6686826323606</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>13.27208211845891</v>
+        <v>107.0663349187037</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>12.64289854739608</v>
+        <v>102.6855825132512</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>12.04779106691909</v>
+        <v>98.51473887849014</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>11.48487659236078</v>
+        <v>94.54278513176295</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.1263059909619966</v>
+        <v>0.801316391482024</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.2025611255842802</v>
+        <v>0.28</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>11.19100238831012</v>
+        <v>96.50147890279625</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>25.78611820799028</v>
+        <v>130.2154056337467</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>1.089841237817762</v>
+        <v>70.4983452970571</v>
       </c>
     </row>
     <row r="59">
@@ -24674,7 +24674,7 @@
         </is>
       </c>
       <c r="B65" s="15" t="n">
-        <v>0.3414956107521308</v>
+        <v>0.2</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         </is>
       </c>
       <c r="B66" s="15" t="n">
-        <v>0.2048973664512785</v>
+        <v>0.1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -25130,7 +25130,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="31" t="inlineStr"/>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25149,7 +25153,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -25157,7 +25161,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr"/>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25176,7 +25184,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -25184,7 +25192,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="31" t="inlineStr"/>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25203,7 +25215,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -25211,7 +25223,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="31" t="inlineStr"/>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
